--- a/Product_Inventory_Template.xlsx
+++ b/Product_Inventory_Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,17 +27,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Kantumruy Pro"/>
+      <name val="Siemreap"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Kantumruy Pro"/>
-      <sz val="10"/>
+      <name val="Siemreap"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Siemreap"/>
+      <color rgb="001E293B"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -46,18 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00107C41"/>
-        <bgColor rgb="00107C41"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
+        <fgColor rgb="00225863"/>
+        <bgColor rgb="00225863"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -67,16 +68,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="001B464F"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="001B464F"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="001B464F"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="001B464F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
       </bottom>
     </border>
   </borders>
@@ -88,14 +103,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,418 +477,280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>កូដទំនិញ (SKU Code)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>ឈ្មោះទំនិញ (Item Name) *</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>កូដទំនិញ/ខ្នាត (Size/Spec) *</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ពណ៌ (Color) *</t>
+          <t>ប្រភេទទំនិញ (Category) *</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ខ្នាត / ម៉ូដែល (Size / Model)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ពណ៌ (Color)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ឯកតារាយ (Retail Unit) *</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ឯកតាដុំ (Pack Unit)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ចំនួនក្នុង១ដុំ (Pack Qty)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>ស្តុកបច្ចុប្បន្ន (Current Stock)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Min Stock %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ឯកតារាយ (Retail Unit) *</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ឯកតាធំ (Bulk Unit)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ចំនួនក្នុង១ដុំ (Pack Rate)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>រូបភាព (Image URL)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ប្រភេទទំនិញ (Category) *</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>កំណត់សម្គាល់ (Notes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+    </row>
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>无线路由器 (Router Wifi)</t>
+          <t>SKU-7501</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>TL-WR940N</t>
+          <t>ប៊ិច-圆珠笔</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>សម្ភារៈការិយាល័យ-办公用品</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Pixcell</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>ខ្មៅ</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>ដើម</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>ប្រអប់</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SKU-9050</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ប៊ិច-圆珠笔</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>សម្ភារៈការិយាល័យ-办公用品</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Pixcell</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>ក្រហម</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ដើម</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ប្រអប់</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SKU-9144</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ទឹកលុប-涂改液</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>សម្ភារៈការិយាល័យ-办公用品</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Pixcell</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ដើម</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>ប្រអប់</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SKU-2089</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ក្រដាសជូតមាត់-抽纸</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ស</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ដុំ</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>យូ</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SKU-2021</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ម៉ាស៊ីនគិតលេខ-计算机</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>សម្ភារៈការិយាល័យ-办公用品</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>19B</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ខ្មៅ</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>គ្រឿង</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ប្រអប់</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>គ្រឿង</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>ប្រអប់</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://images.unsplash.com/photo-1544197150-b99a580bb7a8?w=150</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1ប្រអប់ = 1គ្រឿង</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>外置DVD刻录机 (DVD Drive)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>GP70N</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ស</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>គ្រឿង</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>គ្រឿង</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>ទំនិញរាយ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>电池 (ថ្មពិល AAA)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>AAA-7号</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>បៃតង</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>គ្រាប់</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ប្រអប់</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1ប្រអប់ = 24គ្រាប់</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>电池 (ថ្មពិល 9V)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>9V</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ខ្មៅ</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>គ្រាប់</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>ប្រអប់</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1ប្រអប់ = 10គ្រាប់</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>កាហ្វេ Nescafe 3in1</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>330ml</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ក្រហម</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>កំប៉ុង</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>កេស</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>https://images.unsplash.com/photo-1546868871-7041f2a55e12?w=150</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1កេស = 24កំប៉ុង</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>ក្រដាសជូតមាត់ (Tissue)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ស</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>កញ្ចប់</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>ប្រអប់</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://images.unsplash.com/photo-1586528116311-ad8dd3c8310d?w=150</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1ប្រអប់ = 12កញ្ចប់</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ប៊ិចសរសេរ (Pen)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>0.5mm</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ខៀវ</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ដើម</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>ប្រអប់</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈការិយាល័យ-办公用品</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1ប្រអប់ = 50ដើម</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -887,38 +764,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ល.រ</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ឈ្មោះជួរឈរ (Column)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>លក្ខខណ្ឌ (Requirement)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ការពិពណ៌នា (Description)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ឧទាហរណ៍ (Example)</t>
         </is>
@@ -928,24 +805,24 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ឈ្មោះទំនិញ (Item Name)</t>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>កូដទំនិញ (SKU Code)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ទាមទារចាំបាច់ (*)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ឈ្មោះទំនិញជាភាសាខ្មែរ ចិន ឬអង់គ្លេស</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>无线路由器, កាហ្វេ Nescafe 3in1</t>
+          <t>ស្រេចចិត្ត (Optional)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>កូដសម្គាល់ទំនិញ ឬលេខ Barcode (បើទទេ ប្រព័ន្ធបង្កើតស្វ័យប្រវត្តិ)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>SKU-7501, SKU-9050</t>
         </is>
       </c>
     </row>
@@ -953,9 +830,9 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>កូដទំនិញ/ខ្នាត (Size/Spec)</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ឈ្មោះទំនិញ (Item Name)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -963,14 +840,14 @@
           <t>ទាមទារចាំបាច់ (*)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ទំហំ ខ្នាត ឬម៉ូឌែលទំនិញ (បើគ្មានដាក់ - )</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>TL-WR940N, 330ml, XL, 9V</t>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ឈ្មោះទំនិញជាភាសាខ្មែរ ចិន ឬអង់គ្លេស</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>ប៊ិច-圆珠笔, ទឹកលុប-涂改液</t>
         </is>
       </c>
     </row>
@@ -978,9 +855,9 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>ពណ៌ (Color)</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ប្រភេទទំនិញ (Category)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -988,14 +865,14 @@
           <t>ទាមទារចាំបាច់ (*)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ពណ៌ទំនិញ (បើគ្មានដាក់ ធម្មជាតិ ឬ - )</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>ក្រហម, ស, ខ្មៅ, ខៀវ</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ក្រុមប្រភេទទំនិញតាមស្តង់ដារប្រព័ន្ធ</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>សម្ភារៈការិយាល័យ-办公用品, សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资</t>
         </is>
       </c>
     </row>
@@ -1003,24 +880,24 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>ស្តុកបច្ចុប្បន្ន (Current Stock)</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ខ្នាត / ម៉ូដែល (Size / Model)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>មិនបង្ខំ (ស្រេចចិត្ត)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ចំនួនស្តុកជាក់ស្តែងដែលមានក្នុងដៃ (គិតជាឯកតារាយ) បើទុកទទេប្រព័ន្ធដាក់ 0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8, 4, 30, 132, 0</t>
+          <t>ស្រេចចិត្ត (Optional)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ទំហំ ខ្នាត ឬម៉ូឌែលទំនិញ (បើគ្មានដាក់ -)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Pixcell, LM, 19B, -</t>
         </is>
       </c>
     </row>
@@ -1028,24 +905,24 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Min Stock %</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ពណ៌ (Color)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>មិនបង្ខំ (ស្រេចចិត្ត)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ភាគរយរំលឹកស្តុកទាប (1 ដល់ 100) បើទុកទទេប្រព័ន្ធដាក់ 5%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5, 10, 15</t>
+          <t>ស្រេចចិត្ត (Optional)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ពណ៌សម្គាល់ទំនិញ (បើគ្មានដាក់ -)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>ខ្មៅ, ក្រហម, ស, -</t>
         </is>
       </c>
     </row>
@@ -1053,7 +930,7 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ឯកតារាយ (Retail Unit)</t>
         </is>
@@ -1063,14 +940,14 @@
           <t>ទាមទារចាំបាច់ (*)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>ឯកតាតូចបំផុតសម្រាប់រាប់ ឬបើកចេញ</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>គ្រាប់, ដើម, ដប, កំប៉ុង, គ្រឿង, កញ្ចប់</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ឯកតាតូចបំផុតសម្រាប់រាប់ ឬបើកចេញជាក់ស្តែង</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>ដើម, ដុំ, កញ្ចប់, គ្រឿង, សន្លឹក</t>
         </is>
       </c>
     </row>
@@ -1078,24 +955,24 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>ឯកតាធំ (Bulk Unit)</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ឯកតាដុំ (Pack Unit)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>មិនបង្ខំ (ស្រេចចិត្ត)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ឯកតាជាដុំ ដូចជា កេស ប្រអប់ បាវ យួរ (បើគ្មានដាក់ដូចឯកតារាយ)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>ប្រអប់, កេស, បាវ</t>
+          <t>ស្រេចចិត្ត (Optional)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ឯកតាជាដុំធំ (បើទទេ យកតាមឯកតារាយ)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>ប្រអប់, កេស, យូ, បាច់</t>
         </is>
       </c>
     </row>
@@ -1103,24 +980,24 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>ចំនួនក្នុង១ដុំ (Pack Rate)</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ចំនួនក្នុង១ដុំ (Pack Qty)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>មិនបង្ខំ (ស្រេចចិត្ត)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ចំនួនឯកតារាយក្នុង១ដុំ/កេស (មេគុណបំប្លែង) បើទុកទទេប្រព័ន្ធដាក់ 1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24 (1កេស=24កំប៉ុង), 10, 1</t>
+          <t>ស្រេចចិត្ត (Optional)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ចំនួនឯកតារាយក្នុង១ដុំ (មេគុណបំប្លែង បើទទេដាក់ 1)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>12 (1ប្រអប់=12ដើម), 7, 1</t>
         </is>
       </c>
     </row>
@@ -1128,74 +1005,24 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>រូបភាព (Image URL)</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ស្តុកបច្ចុប្បន្ន (Current Stock)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>មិនបង្ខំ (ស្រេចចិត្ត)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Link រូបភាពទំនិញ បើគ្មានប្រព័ន្ធដាក់រូបស្វ័យប្រវត្តិ</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://...</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>ប្រភេទទំនិញ (Category)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>ទាមទារចាំបាច់ (*)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>ប្រភេទក្រុមទំនិញ</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>សម្ភារៈប្រើប្រាស់ទូទៅ-常用物资, សម្ភារៈការិយាល័យ-办公用品</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>កំណត់សម្គាល់ (Notes)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>មិនបង្ខំ (ស្រេចចិត្ត)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>កំណត់សម្គាល់ផ្សេងៗ បើគ្មានដាក់ -</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>ស្រេចចិត្ត (Optional)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ចំនួនស្តុកជាក់ស្តែងដែលមានក្នុងដៃ (គិតជាឯកតារាយ បើទទេដាក់ 0)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>95, 0, 5, 120</t>
         </is>
       </c>
     </row>
